--- a/research/traditional_assets/database/data/pakistan/pakistan_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_homebuilding.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.264</v>
+        <v>0.328</v>
       </c>
       <c r="E2">
-        <v>1.115</v>
+        <v>1.061</v>
       </c>
       <c r="G2">
-        <v>0.2018181818181818</v>
+        <v>0.2682634730538923</v>
       </c>
       <c r="H2">
-        <v>0.2018181818181818</v>
+        <v>0.2682634730538923</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>0.2455089820359281</v>
       </c>
       <c r="J2">
-        <v>0.22</v>
+        <v>0.2115154306771073</v>
       </c>
       <c r="K2">
-        <v>4.23</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>0.2563636363636364</v>
+        <v>0.2215568862275449</v>
       </c>
       <c r="M2">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="N2">
-        <v>0.1173410404624278</v>
+        <v>0.1857988165680474</v>
       </c>
       <c r="O2">
-        <v>0.4799054373522459</v>
+        <v>0.8486486486486486</v>
       </c>
       <c r="P2">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="Q2">
-        <v>0.1173410404624278</v>
+        <v>0.1857988165680474</v>
       </c>
       <c r="R2">
-        <v>0.4799054373522459</v>
+        <v>0.8486486486486486</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.27</v>
+        <v>0.351</v>
       </c>
       <c r="V2">
-        <v>0.07341040462427745</v>
+        <v>0.02076923076923077</v>
       </c>
       <c r="W2">
-        <v>0.6900489396411094</v>
+        <v>0.296</v>
       </c>
       <c r="X2">
-        <v>0.1579366225694498</v>
+        <v>0.2235499893781714</v>
       </c>
       <c r="Y2">
-        <v>0.5321123170716595</v>
+        <v>0.07245001062182868</v>
       </c>
       <c r="Z2">
-        <v>3.211366290385364</v>
+        <v>1.853496115427303</v>
       </c>
       <c r="AA2">
-        <v>0.7065005838847801</v>
+        <v>0.3920430291129514</v>
       </c>
       <c r="AB2">
-        <v>0.1579366225694498</v>
+        <v>0.2235499893781714</v>
       </c>
       <c r="AC2">
-        <v>0.5485639613153303</v>
+        <v>0.1684930397347801</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.27</v>
+        <v>-0.351</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,22 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0792264504054897</v>
+        <v>-0.02120974076983503</v>
       </c>
       <c r="AK2">
-        <v>-0.1111111111111111</v>
+        <v>-0.03563813585135547</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.3307291666666667</v>
+        <v>-0.07834821428571427</v>
+      </c>
+      <c r="AQ2">
+        <v>-67.21311475409836</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.264</v>
+        <v>0.328</v>
       </c>
       <c r="E3">
-        <v>1.115</v>
+        <v>1.061</v>
       </c>
       <c r="G3">
-        <v>0.2018181818181818</v>
+        <v>0.2682634730538923</v>
       </c>
       <c r="H3">
-        <v>0.2018181818181818</v>
+        <v>0.2682634730538923</v>
       </c>
       <c r="I3">
-        <v>0.22</v>
+        <v>0.2455089820359281</v>
       </c>
       <c r="J3">
-        <v>0.22</v>
+        <v>0.2115154306771073</v>
       </c>
       <c r="K3">
-        <v>4.23</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>0.2563636363636364</v>
+        <v>0.2215568862275449</v>
       </c>
       <c r="M3">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="N3">
-        <v>0.1173410404624278</v>
+        <v>0.1857988165680474</v>
       </c>
       <c r="O3">
-        <v>0.4799054373522459</v>
+        <v>0.8486486486486486</v>
       </c>
       <c r="P3">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>0.1173410404624278</v>
+        <v>0.1857988165680474</v>
       </c>
       <c r="R3">
-        <v>0.4799054373522459</v>
+        <v>0.8486486486486486</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.27</v>
+        <v>0.351</v>
       </c>
       <c r="V3">
-        <v>0.07341040462427745</v>
+        <v>0.02076923076923077</v>
       </c>
       <c r="W3">
-        <v>0.6900489396411094</v>
+        <v>0.296</v>
       </c>
       <c r="X3">
-        <v>0.1579366225694498</v>
+        <v>0.2235499893781714</v>
       </c>
       <c r="Y3">
-        <v>0.5321123170716595</v>
+        <v>0.07245001062182868</v>
       </c>
       <c r="Z3">
-        <v>3.211366290385364</v>
+        <v>1.853496115427303</v>
       </c>
       <c r="AA3">
-        <v>0.7065005838847801</v>
+        <v>0.3920430291129514</v>
       </c>
       <c r="AB3">
-        <v>0.1579366225694498</v>
+        <v>0.2235499893781714</v>
       </c>
       <c r="AC3">
-        <v>0.5485639613153303</v>
+        <v>0.1684930397347801</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.27</v>
+        <v>-0.351</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,22 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0792264504054897</v>
+        <v>-0.02120974076983503</v>
       </c>
       <c r="AK3">
-        <v>-0.1111111111111111</v>
+        <v>-0.03563813585135547</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.3307291666666667</v>
+        <v>-0.07834821428571427</v>
+      </c>
+      <c r="AQ3">
+        <v>-67.21311475409836</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_homebuilding.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.328</v>
+        <v>0.263</v>
       </c>
       <c r="E2">
-        <v>1.061</v>
+        <v>0.248</v>
       </c>
       <c r="G2">
-        <v>0.2682634730538923</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="H2">
-        <v>0.2682634730538923</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="I2">
-        <v>0.2455089820359281</v>
+        <v>0.2082089552238806</v>
       </c>
       <c r="J2">
-        <v>0.2115154306771073</v>
+        <v>0.119736779361976</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="L2">
-        <v>0.2215568862275449</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="M2">
-        <v>3.14</v>
+        <v>0.539</v>
       </c>
       <c r="N2">
-        <v>0.1857988165680474</v>
+        <v>0.01911347517730497</v>
       </c>
       <c r="O2">
-        <v>0.8486486486486486</v>
+        <v>0.2994444444444445</v>
       </c>
       <c r="P2">
-        <v>3.14</v>
+        <v>0.539</v>
       </c>
       <c r="Q2">
-        <v>0.1857988165680474</v>
+        <v>0.01911347517730497</v>
       </c>
       <c r="R2">
-        <v>0.8486486486486486</v>
+        <v>0.2994444444444445</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.351</v>
+        <v>0.045</v>
       </c>
       <c r="V2">
-        <v>0.02076923076923077</v>
+        <v>0.001595744680851064</v>
       </c>
       <c r="W2">
-        <v>0.296</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="X2">
-        <v>0.2235499893781714</v>
+        <v>0.2244234164766464</v>
       </c>
       <c r="Y2">
-        <v>0.07245001062182868</v>
+        <v>-0.0479528282413523</v>
       </c>
       <c r="Z2">
-        <v>1.853496115427303</v>
+        <v>1.360544217687075</v>
       </c>
       <c r="AA2">
-        <v>0.3920430291129514</v>
+        <v>0.1629071828054096</v>
       </c>
       <c r="AB2">
-        <v>0.2235499893781714</v>
+        <v>0.2244234164766464</v>
       </c>
       <c r="AC2">
-        <v>0.1684930397347801</v>
+        <v>-0.06151623367123685</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.351</v>
+        <v>-0.045</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.02120974076983503</v>
+        <v>-0.00159829515183804</v>
       </c>
       <c r="AK2">
-        <v>-0.03563813585135547</v>
+        <v>-0.005291005291005291</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.061</v>
+        <v>-0.049</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.07834821428571427</v>
+        <v>-0.01451612903225806</v>
       </c>
       <c r="AQ2">
-        <v>-67.21311475409836</v>
+        <v>-56.93877551020408</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.328</v>
+        <v>0.263</v>
       </c>
       <c r="E3">
-        <v>1.061</v>
+        <v>0.248</v>
       </c>
       <c r="G3">
-        <v>0.2682634730538923</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="H3">
-        <v>0.2682634730538923</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="I3">
-        <v>0.2455089820359281</v>
+        <v>0.2082089552238806</v>
       </c>
       <c r="J3">
-        <v>0.2115154306771073</v>
+        <v>0.119736779361976</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="L3">
-        <v>0.2215568862275449</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="M3">
-        <v>3.14</v>
+        <v>0.539</v>
       </c>
       <c r="N3">
-        <v>0.1857988165680474</v>
+        <v>0.01911347517730497</v>
       </c>
       <c r="O3">
-        <v>0.8486486486486486</v>
+        <v>0.2994444444444445</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>0.539</v>
       </c>
       <c r="Q3">
-        <v>0.1857988165680474</v>
+        <v>0.01911347517730497</v>
       </c>
       <c r="R3">
-        <v>0.8486486486486486</v>
+        <v>0.2994444444444445</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.351</v>
+        <v>0.045</v>
       </c>
       <c r="V3">
-        <v>0.02076923076923077</v>
+        <v>0.001595744680851064</v>
       </c>
       <c r="W3">
-        <v>0.296</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="X3">
-        <v>0.2235499893781714</v>
+        <v>0.2244234164766464</v>
       </c>
       <c r="Y3">
-        <v>0.07245001062182868</v>
+        <v>-0.0479528282413523</v>
       </c>
       <c r="Z3">
-        <v>1.853496115427303</v>
+        <v>1.360544217687075</v>
       </c>
       <c r="AA3">
-        <v>0.3920430291129514</v>
+        <v>0.1629071828054096</v>
       </c>
       <c r="AB3">
-        <v>0.2235499893781714</v>
+        <v>0.2244234164766464</v>
       </c>
       <c r="AC3">
-        <v>0.1684930397347801</v>
+        <v>-0.06151623367123685</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.351</v>
+        <v>-0.045</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02120974076983503</v>
+        <v>-0.00159829515183804</v>
       </c>
       <c r="AK3">
-        <v>-0.03563813585135547</v>
+        <v>-0.005291005291005291</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.061</v>
+        <v>-0.049</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.07834821428571427</v>
+        <v>-0.01451612903225806</v>
       </c>
       <c r="AQ3">
-        <v>-67.21311475409836</v>
+        <v>-56.93877551020408</v>
       </c>
     </row>
   </sheetData>
